--- a/inputs/es/template_input.xlsx
+++ b/inputs/es/template_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{683CEACF-E93B-4540-A560-587D7A152A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3305AE83-31BA-4766-BC0F-9E83ABF198C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Distribución estado nutricional" sheetId="4" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="5" r:id="rId5"/>
     <sheet name="Tendencias temporales" sheetId="6" r:id="rId6"/>
-    <sheet name="Variables económicas   " sheetId="7" r:id="rId7"/>
+    <sheet name="Variables económicas" sheetId="7" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="8" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="9" r:id="rId9"/>
     <sheet name="Costo y cobertura del programa" sheetId="10" r:id="rId10"/>
@@ -20622,6 +20622,35 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="aeiFifHTTUBFQteGhzKvj8LLcRbrvkLb8nHMonN+5ynj/NW3dZFdNu5ZC76LPvJS++4fCtkHWhNX+uBGQ87JBA==" saltValue="OGRa/cx1fprbCBKPGO79iQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B142:B144"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B111:B113"/>
@@ -20638,35 +20667,6 @@
     <mergeCell ref="B98:B100"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -41177,16 +41177,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -41370,6 +41360,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -41380,16 +41380,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41407,6 +41397,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
   <ds:schemaRefs>

--- a/inputs/es/template_input.xlsx
+++ b/inputs/es/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23730082-8BB5-49C4-9719-8AE758D95A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB9B094-2B97-4C1B-A49B-26BB70394CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -9845,7 +9845,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Uskp53gz04eem8xWglaqKP4Vlvl/mwWr26pMkG81eYJf7CRjbzSBgf8F/03RaLY1VWj4EwDv8H7IookuU7d8IQ==" saltValue="XzhafPvZ7ajQMMJx2fCNZw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="e+3Nchjdzm1KstZvKAzE3aV8Kgbu83h8WnqutrA6r/Wem5HPixJoS+Fe02CrXGFb5BaeDfK0EdaZbxzIUF1NQQ==" saltValue="/nX9ySayESo5UTiiE8+wsg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10770,7 +10770,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NbHQb8NTIlfEU+TYA7E0b4S9KctAbdiMZK7BiI8o1YvsjHjKfeQMp7L/t5EgO096irI5JiA6XzZUsFrCIP9W3w==" saltValue="LIHmX0Ob1y9j63JBecudWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FP/NDxH8rtmuYSLs/Mm93EEk+Pgvam7gCYMHYWxOciXlfjg56mf96iF73w8GBbOfwOFH6zR0z1JXhRR/QR3S5g==" saltValue="1kGl5GndM9cUushY2Rv2Jg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10923,7 +10923,7 @@
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+yECtSJUrJcQjWrdDnJzPyL0JTg1bLsmNca24UG2cI4aqxUvdE+fVAcM2FA4Tn725WLqsL1q7Q3Jm19bEuZeyQ==" saltValue="19rpcGzK0LXWefoaCkzxNQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="chyxyU++un48dieilMxycNIPcZbNz0j8SCTS015Ux9ROywgXfNdqZcnlzqBX6OVW5tpc3wD/KYtw7EZ7RP+BXg==" saltValue="Em4VG+gaYyGxAyMuJ/8QEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -11021,7 +11021,7 @@
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QMFuwcslIIqmgCv/HxXQij1lU0JsxLhz10nAQ/Xh+0g4+QSl0tCxKD8yotzG1gTud78cl/ROXFCe+hDdeVJ88Q==" saltValue="vB3xumGDGRqisvj+1R6REw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="COWXfANdL2P8vqtpd06QCG06XfaUi+JScyuL1VBWe4MdWFml4b35ZAte4CqpJ7GAlXnHm+r3MXUtj2zIKC+LKg==" saltValue="Xp9uWKjuVaFocVyUsud2Yg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -11131,7 +11131,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rurr3SLIOKFT23o/fQoAfp0elb0VeExPXNvDS9GQBMCG7ztf0D3oWqAcIFezdORr5vbRqSnW7dlfP2RkFztzjA==" saltValue="GqtVOx8C/re0cbGaQuuzHw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vbM1qbrFqLoHfBiOVEZccElROfaCXHn/7qnXBo9wNtQdZ3tSJBf+qz2kXeATUO5L6q8MY6Ve44upL8IJfWqMlQ==" saltValue="xXt1YJ/WVfVQ4ZJn84TUnQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12889,7 +12889,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="syOJSu/5F/IUfQ95PFe0mCHnMauOkcx/HadQIXUco7G4FhqP5SKzEQjoEMm3GL1aeFua8eJYU/4l1BW/CuBrXQ==" saltValue="OU3vP9K16uTETM8zlm6baw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HEgZOSFPvPC0L2xfbnPosVbswxnNuTaMIRY1dyrVFU+2dAcSyxh2+SK1qH34txLDHSNtEnux12n8EgVCuV42Fg==" saltValue="36vX/0PH9NO4B59mqKsH2w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12922,7 +12922,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cCK2CZyNQvX7WFyY8Ucq32rEtjgWL1CX1GstcBArTNzru1iJabgFCzPhBq5SAIzNtUnhUtpQgZpUVUggRIwq8A==" saltValue="dB5NYX7mLQzhExf6sDTgqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1Zw92sEDnMnJiWEhu8u9AJPlIvPkJ8I/r1tN+9aRJ4w8r2triRmYqxRT4bT3IfHz9NjNM6SMk2iqWDm3LOd9zw==" saltValue="05B2N70uy42TVwUey03UNg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13123,7 +13123,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="x6VAeq0aTnFbX1pri2uypakYzZRXGSnbXgR5ynsFbbI0DMZbpOlxsVRDy8vEEai5PVYTkSDeH6KXG/dFjsCp2w==" saltValue="EpcYnxWUE+R+sJWb3JHsdw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ishuYTWTdE7V2eKtr9Q6GG6KZhDvZA3tvcvn1+FAQt+NKbLXznukiNMibAgu8ZG3ZqTYCy5rpmsDuvsqtLIRNw==" saltValue="RqKwZ4i+MQlyCXFTkRmMXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14933,7 +14933,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3JXQMEDR0UJhsobjrkma4TFtgDRTAqYgs4BophwdWfpnLn2rfH6+OrWm1wKHP7JPjntjho4Z1vIYVYC6BSMp7w==" saltValue="i4l5zs4Ur9v1TFd10TDsHg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="u2S5eOFiw1oSjafYZoHH5V/eqIh4LPJIzFB6+WzxkE5DOsYzAcZRmlveh9qsTRbd55vrI9szLVMwWMvIkKdf/Q==" saltValue="EW3DfKkjAZF0ozxTo9xZEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15744,7 +15744,7 @@
       <c r="L39" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="c0DcvitfGpldhC2lv3vGSlm8jAjtm1HCJm6f1vsgGDZ9aYGOk7AI3cLlo26MsSNM90mHy/SmWRS+ZCt40YHf/g==" saltValue="EeYTGfRV2C/cgFLv4+/YMg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="P1FibpIN/J5m2+pbmKW4hH40lDb5aO4KmfzN/AiK0P7rClPlWYKbFW+qKgQGlOGhS6yCjFO68Pxyx28NUUdU8g==" saltValue="GJTfmZjxAQRTNSalx10mHA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16137,7 +16137,7 @@
       <c r="L14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Zn0IzmyrBqr5eUBYONv6TfATJevpLNjs/MssVzuzYd+pP3/HqnvPeBnzLoZKMguL2qr36uvrmesxeGlRXGB5xA==" saltValue="hcLwH18ad8YiOuO4cdSk0g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8BbdP4+uZHVzRG/xnHGHbWv4sSCLSdtYTpkpc9ASRZB+TjuyGTKQpWQDvuHQdXlH7x92wtkvhWqnPU22JvYYxg==" saltValue="wJDRiqQl3Sh2Gq7uVQluUw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16866,7 +16866,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rfYnGVqTfCfDI1tOatqoEqBdChm6m1q09YzlisHBLyZfgnRBjSxgXp2W03MdGPj8YkFYxN9eKjINkM8zHZaHhA==" saltValue="E6jY3Z39G4lEZxcvVoPQ6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kHrWG3KLiQ+Bor3jZwhrTd696HOBxnMKQLCQGA1CeDSazpMxotHpVJLdK0LZqPFGfyGK73/2YE6PzceKc8MvBQ==" saltValue="ySGjgM6OljkXwUaQutwtLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -20663,7 +20663,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NA3l0U7UfvNpNYDfWHJzmm4ahbvxesvsqvMQ741y6aS7pfzoC7qbQ2Ybh07/6JGfm+gytLO7fCZXruuYwyen3w==" saltValue="/KVryiXdZ2aBgdSPtU2uPg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/mj7Z8jnBwA6a/RdXUC6tcw82DDcFmfyEvBkRdeLLcv53wDibXzymi/M+I+Hv5JoPUQZlJDhSvxHl0+m+90RIA==" saltValue="qWwvtHpclAVH96pBunCv9w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B36:B38"/>
@@ -21810,7 +21810,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QIwXUxURNbbq2EP1aHNBYaFVEiiLzzrz419AsMiqGERimg4lyKxG5VOVvo7t9epSjsAEKkYDhIeZNqHILZLtEA==" saltValue="arwVdGOTGX1qNtouIJPxiw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vPfb9kQB/wJd63Nrv25TBqB602YrPvGsnBJmCPdBMK8jD5uAIPt2gXKxattFPi81IJmzpxPm/XSd7lHeRAbJmA==" saltValue="+u0hb/iySmj5Mmuest7zng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -22751,7 +22751,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a+8CsmRY9zas80phjpe9gtx1ZQ7KCMmaDT/KwNqZAuRoBoweoprkrFkDof5QxZKzn4LOBYthdlXn959/e27GtQ==" saltValue="F5tkf0ohTEqElz7w1juRDw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Y2j2on0Oe2xh9rgTy+NbH9FLTB3OORRx7KcagQKCYfIFXzSe/fPLqenCn/fpDLFayXUP9LGmiC2BbLpkkpX4zw==" saltValue="QWhjn1fh8DsjpDdd/1jfIQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -23967,7 +23967,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/wjKhxqokvB/3/5amhEy8JLTl7Q6E9iWbBNMdbUrPXt2wTIZ8IqqI72N9IkSYhJJwsnVE/78i3FVqUunLLeOvw==" saltValue="TP+zDkQrcwjgb5FpD+IKqw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LlxXYRl2dylqsvgEtlcXchj6mMF2ppQpK6FdJFxWVeQDvM9gUC3Y77GcIuJrq1WtqHreFiTZVRiJbR9Sm/ZLtw==" saltValue="7QhX2tRHqQ4b9Z3ot3j0mg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -32102,7 +32102,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZDwWOJtL3eJ69jc4dBuBiZ61Scmae+E2qBO3dIDiDe0XiyST4QN8FEG4+exU90VolrYhESbOuUfaRsfq4nPaJg==" saltValue="pqbk7DV/BE2CIrkY93o3XQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ahIptCMoHT1HGH63297HC6hp/jO6XzHUiygdOBV95xxJucdz5eaEfWJNWDfbJwQSZf0tDQQebSQJN1STw8kNPQ==" saltValue="kmde3W22itqn9md/cbkL1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34792,7 +34792,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MrYP3LQdiKF/XyLbAQWTuFsWBH3bhP0/zx1m7+LVfuACEvIL0RK6gOkDJpHd6tkTOqN9yn+YI88GWmIsup/4gw==" saltValue="gVmMLg7F6m9ChCe/CqRDJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="m2DHxwHv5mL+qUwDWOZ60Qdpe1iZ1HBGAndmFFLUjIM6tJ4B+qz3jDdoyEpB66UwWcmehZsVxF2We/A3Pkfkyg==" saltValue="jT1mxSNvHc0NaAlbgLch6Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35074,7 +35074,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vYQfw5rrAfMjmyBUiC2ummgqrzhVosjtRfKMzAIr7zre5o2xjnBJmLSogPtItcGgKptk03pF8ZwVTa/EIxeonw==" saltValue="H/zmkkEVe6Np5mMooWlMPA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZpOhgV7xesjvBhyYUwJ/kHGa3wwnr613XrLotIs/N6ej7s/dCHESihnrxiNVIS5chQoWpIFZCWidltenyd7cBg==" saltValue="hChUm6B6vdUTQl2GdccHWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -38934,7 +38934,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jLBkb2f269RMa96A09d7O0VrH2oNGX9V81uHLCI1bfs23h1YgvlAXHvLg1ZJRI+UbNEeMN/0in5LJNrhxSV2Tw==" saltValue="GhkKAMdcgtr9OSHrMRBVbg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TZK398QYGxHlEIBCYznmAqQMVDvCCojz+IS2iO+oI4vcKPalyNPzgYzV4sR95fN0l/NLDsyd/5bsCAsEvaxx3w==" saltValue="J3vdvVs5DQCmKBF+86y+YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39574,7 +39574,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="A7RO7k7NKOiv+gUKC2FXi0I6H81XwBYSu2lvaqZE37jBMCS5j3DNCJk/mAQJ0A88DTN8G/KPFNfOXJVDBB4CQg==" saltValue="LBLHV5Tvd6295zxFNg3UiA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4vIEaBMmGL60/742opUA5P5tmQHbfCm9lyu7wWucyNWbEWe5PYw7Fy3hFRbSzFjPzfKUIEuTpyc+//36HaalXA==" saltValue="jelZKU4rUFckgKRyTNPjHg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39901,7 +39901,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UQtoMuK4zA3nT00O+ivPq5KrWfEDq0xTy0gWJsObd/pP7iyrk9G6Q6ye/n/GpsCirIRiCNXpqkrZVn6IdvurGA==" saltValue="6SxoRxmvXcHoZToN6wqgPA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5ZgKyhTOs9cP8Zz8ZeZN7tfwJZf9uh6GH/y6DYYVVEUS7vp90N4z/XKTQMZ2U9Pr7cVWoFyU6QSplzG9ose1ZQ==" saltValue="pS39h4a98UIFJssNAOopLg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40254,7 +40254,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Wf+5+ukU60RozObGQcCxy6/OjUlWhGjj/7sTgS5eiWWVfyFjEJFkLFUU7t3flfUCndhRNYXuIY7tVPNLqHNBHg==" saltValue="D643YpLh6gfo+BJzD8geow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RXqPMJp5A4N7WYsVrfP6PxzLY/ummCAxe3TcyayPLKS5nwvQogMaQzB2QQei9i3RY8rCxugCF59ef0+hnyMbOQ==" saltValue="QgyzX/8AQlKegmopMcIwiw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40370,7 +40370,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9ijSE/8BUkAXVkYi65EZ1XPappPDy481N5Wqs6l7s9jtn5e4kG7Ye/HhFem8K/3f/oD6u0fBZ3SUcgAhKme2Dg==" saltValue="3AxUIhvBa1aD17M9MMnGAg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="g+kd5maLZOcJqeXzPknncKRFsWsVTq3MK3ZZNKaZr9ye1BAInJTEUdWtYhQp0XK8uOMxqmaJU+WRsqGCkHL4Iw==" saltValue="IpX0G5CbuGYmfm03gGytYg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40571,7 +40571,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UETelxuuUOU2OC1FXO4qSULaQEabOv3RLLn+1LKkQWEY/YyRTegoLKYRD9e9B7/0iV/fe2Fypjzzroia/IYE+A==" saltValue="fxbMB5DizBMvSnafUYlfOw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HeXCcx/Tfuh/HBo2OV1NfCrMCHaB4AucOkTq5YjrKtoHBeHxF9FnjYab5pp6TUJ5TKYwEIW8HccU8oMrkNxK1A==" saltValue="v3ZRt/as+V9miKXYhPI04A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -41034,7 +41034,7 @@
       <c r="O22" s="107"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z6/b1/imxgPDzoi38JdYGPRBqdygZPS6AZDeDCgZ2iMheGuhkd8vJEB7HJS3Q72hDjBVoX70YXcKOyMFlN9Ikw==" saltValue="zQTPQ1NHbBiuKjFwYxG41Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UHHzvQw/HaJ00FVwFicnwMMUvj+JVnEmcv+rVoUBv2LlcJZ4VmPc3l6w6pu6+LeGFv21t3gfJxeCwubmdAeSmw==" saltValue="OgMN9c1C8EDsSwHd0XtKbg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41293,7 +41293,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="W5XzgL4kpq+OJzQqZb+zhCDzi74wZOXb0UdJwnkFuQf6kBegXKHGV1sEZvmd2kCnBgO+d7SaZjsGi0Sk+4vZRg==" saltValue="4ZDPkjjBfddnzQ3wmhMWDw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Jo4eeDHx2pRRR7L6sRMKPYLMKA1GZymJL+zS3ntxI9ab3ir1PJ5rb6NuHPcOF6Fn+sC4FHKJK6mvqheLZlBLAg==" saltValue="5GypOhOrBKI1qS8frX0XtQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -41352,7 +41352,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xk6S0VAAMLtTo7bPuml0sR6KtVIGEuDxVJvEihFF9KlMpz9/bCDwNdn+TjG4AXjY+TFq5yUYt3vD/5pgDMXLEA==" saltValue="twCLg8ASStPVp0T9z9qATQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2fnuTUQp9C02tmYptGKjbSRZD9JLXBgEHmX2hsG4XMy7EFh06RwF1HjUxVDt6AuWvikzqn+CmqRl9AoVHv+wOg==" saltValue="tb36qr75rkJOdjK95UmR2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
